--- a/2d/results/best_unet_nofilter_distance_max/best_unet.xlsx
+++ b/2d/results/best_unet_nofilter_distance_max/best_unet.xlsx
@@ -535,55 +535,55 @@
         <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>13.3029259253122</v>
+        <v>21.09374320733217</v>
       </c>
       <c r="D2" t="n">
-        <v>21.09374419375769</v>
+        <v>13.30294298233676</v>
       </c>
       <c r="E2" t="n">
-        <v>39.13692850022633</v>
+        <v>39.13692454852634</v>
       </c>
       <c r="F2" t="n">
-        <v>13.21549256078324</v>
+        <v>13.21549415010245</v>
       </c>
       <c r="G2" t="n">
-        <v>10.62963138580692</v>
+        <v>10.62962921262072</v>
       </c>
       <c r="H2" t="n">
-        <v>77.87706492722732</v>
+        <v>77.87708636607368</v>
       </c>
       <c r="I2" t="n">
-        <v>74.03852946735977</v>
+        <v>74.03851376343123</v>
       </c>
       <c r="J2" t="n">
-        <v>65.49213393197319</v>
+        <v>65.49213019300997</v>
       </c>
       <c r="K2" t="n">
         <v>63.97595014493935</v>
       </c>
       <c r="L2" t="n">
-        <v>38.28121370613754</v>
+        <v>38.28120703724467</v>
       </c>
       <c r="M2" t="n">
-        <v>31.38765500992137</v>
+        <v>31.38765660550638</v>
       </c>
       <c r="N2" t="n">
-        <v>73.70863862665153</v>
+        <v>73.70866145465294</v>
       </c>
       <c r="O2" t="n">
-        <v>62.27465730715297</v>
+        <v>62.27465460974342</v>
       </c>
       <c r="P2" t="n">
-        <v>21.85435538982104</v>
+        <v>21.85433547257408</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.51555447847583</v>
+        <v>21.51553533387082</v>
       </c>
       <c r="R2" t="n">
-        <v>21.16819523132147</v>
+        <v>21.16817689730326</v>
       </c>
       <c r="S2" t="n">
-        <v>22.4076430404616</v>
+        <v>22.40762501926205</v>
       </c>
     </row>
     <row r="3">
@@ -596,55 +596,55 @@
         <v>141</v>
       </c>
       <c r="C3" t="n">
-        <v>16.66209211099801</v>
+        <v>14.07204574262149</v>
       </c>
       <c r="D3" t="n">
-        <v>14.07203798270239</v>
+        <v>16.66209351760326</v>
       </c>
       <c r="E3" t="n">
-        <v>30.12154261328451</v>
+        <v>30.12152511261824</v>
       </c>
       <c r="F3" t="n">
-        <v>21.5731424838683</v>
+        <v>21.57314276702556</v>
       </c>
       <c r="G3" t="n">
-        <v>16.28924936605909</v>
+        <v>16.28925020805655</v>
       </c>
       <c r="H3" t="n">
-        <v>81.92009362938725</v>
+        <v>81.92008146025468</v>
       </c>
       <c r="I3" t="n">
-        <v>88.8511864089172</v>
+        <v>88.85117512175206</v>
       </c>
       <c r="J3" t="n">
-        <v>71.9686134082469</v>
+        <v>71.96862696943931</v>
       </c>
       <c r="K3" t="n">
-        <v>78.61142534714904</v>
+        <v>78.61144599036822</v>
       </c>
       <c r="L3" t="n">
-        <v>55.34586647887329</v>
+        <v>55.34586659500744</v>
       </c>
       <c r="M3" t="n">
-        <v>44.86436124537023</v>
+        <v>44.8643609236608</v>
       </c>
       <c r="N3" t="n">
-        <v>80.97744314367786</v>
+        <v>80.97742646228639</v>
       </c>
       <c r="O3" t="n">
-        <v>71.71698069281199</v>
+        <v>71.71697127077459</v>
       </c>
       <c r="P3" t="n">
-        <v>14.86715404229322</v>
+        <v>14.86715649253281</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.3167921759773</v>
+        <v>14.31677430203544</v>
       </c>
       <c r="R3" t="n">
-        <v>15.40497591939227</v>
+        <v>15.40495430792459</v>
       </c>
       <c r="S3" t="n">
-        <v>14.34458856670933</v>
+        <v>14.34455648309993</v>
       </c>
     </row>
     <row r="4">
@@ -657,55 +657,55 @@
         <v>149</v>
       </c>
       <c r="C4" t="n">
-        <v>9.455972305633663</v>
+        <v>13.03125900529935</v>
       </c>
       <c r="D4" t="n">
-        <v>13.03125589216001</v>
+        <v>9.45598634141518</v>
       </c>
       <c r="E4" t="n">
-        <v>17.31703756694764</v>
+        <v>17.31701013922459</v>
       </c>
       <c r="F4" t="n">
-        <v>11.2291310475026</v>
+        <v>11.22912802349719</v>
       </c>
       <c r="G4" t="n">
-        <v>9.326822485151069</v>
+        <v>9.326817311775152</v>
       </c>
       <c r="H4" t="n">
-        <v>83.69717230193145</v>
+        <v>83.69718964011237</v>
       </c>
       <c r="I4" t="n">
-        <v>74.63557867942332</v>
+        <v>74.63558777453079</v>
       </c>
       <c r="J4" t="n">
-        <v>71.66145464944898</v>
+        <v>71.6614535018517</v>
       </c>
       <c r="K4" t="n">
-        <v>64.94639205716928</v>
+        <v>64.94638504604262</v>
       </c>
       <c r="L4" t="n">
-        <v>33.62715312965157</v>
+        <v>33.62716769626645</v>
       </c>
       <c r="M4" t="n">
-        <v>27.22987619609826</v>
+        <v>27.22986554358513</v>
       </c>
       <c r="N4" t="n">
-        <v>77.49978667213431</v>
+        <v>77.49978497686874</v>
       </c>
       <c r="O4" t="n">
-        <v>66.85769837119388</v>
+        <v>66.85770206357471</v>
       </c>
       <c r="P4" t="n">
-        <v>15.20900396688174</v>
+        <v>15.20904098421551</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.95762235165669</v>
+        <v>16.95764456857335</v>
       </c>
       <c r="R4" t="n">
-        <v>18.92710557768742</v>
+        <v>18.92711162045243</v>
       </c>
       <c r="S4" t="n">
-        <v>17.27671070860287</v>
+        <v>17.27672421671475</v>
       </c>
     </row>
     <row r="5">
@@ -718,55 +718,55 @@
         <v>160</v>
       </c>
       <c r="C5" t="n">
-        <v>16.29399833705625</v>
+        <v>18.81242028199514</v>
       </c>
       <c r="D5" t="n">
-        <v>18.81242998592574</v>
+        <v>16.2939981911419</v>
       </c>
       <c r="E5" t="n">
-        <v>41.62514299124299</v>
+        <v>41.62518046665494</v>
       </c>
       <c r="F5" t="n">
-        <v>11.35221674782552</v>
+        <v>11.3522132283097</v>
       </c>
       <c r="G5" t="n">
-        <v>8.307197996997713</v>
+        <v>8.30719886297986</v>
       </c>
       <c r="H5" t="n">
-        <v>69.13085121911764</v>
+        <v>69.13087333193704</v>
       </c>
       <c r="I5" t="n">
-        <v>67.95498743519587</v>
+        <v>67.95497381653001</v>
       </c>
       <c r="J5" t="n">
-        <v>55.210067794065</v>
+        <v>55.21008479125257</v>
       </c>
       <c r="K5" t="n">
-        <v>53.53137345742825</v>
+        <v>53.5313800715035</v>
       </c>
       <c r="L5" t="n">
-        <v>35.79699704406016</v>
+        <v>35.7969946142569</v>
       </c>
       <c r="M5" t="n">
-        <v>30.07591674271859</v>
+        <v>30.07591398332083</v>
       </c>
       <c r="N5" t="n">
-        <v>66.46436891529589</v>
+        <v>66.46435427304205</v>
       </c>
       <c r="O5" t="n">
-        <v>51.69721082568807</v>
+        <v>51.69721599321068</v>
       </c>
       <c r="P5" t="n">
-        <v>26.04479466247859</v>
+        <v>26.0447929288536</v>
       </c>
       <c r="Q5" t="n">
-        <v>25.09505019390835</v>
+        <v>25.09502716120723</v>
       </c>
       <c r="R5" t="n">
-        <v>24.89936928268275</v>
+        <v>24.89938973866251</v>
       </c>
       <c r="S5" t="n">
-        <v>26.13959828858165</v>
+        <v>26.13955152348878</v>
       </c>
     </row>
     <row r="6">
@@ -779,55 +779,55 @@
         <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>9.398521035353392</v>
+        <v>15.56110860044728</v>
       </c>
       <c r="D6" t="n">
-        <v>15.56111660638908</v>
+        <v>9.398520427061918</v>
       </c>
       <c r="E6" t="n">
-        <v>24.95312556241898</v>
+        <v>24.95307474774778</v>
       </c>
       <c r="F6" t="n">
-        <v>15.29998482076749</v>
+        <v>15.29997552208817</v>
       </c>
       <c r="G6" t="n">
-        <v>11.48216039741033</v>
+        <v>11.48216119367439</v>
       </c>
       <c r="H6" t="n">
-        <v>80.51634809176808</v>
+        <v>80.51634159812075</v>
       </c>
       <c r="I6" t="n">
-        <v>75.59966448615809</v>
+        <v>75.59966987288064</v>
       </c>
       <c r="J6" t="n">
-        <v>57.79639048017537</v>
+        <v>57.7964081450495</v>
       </c>
       <c r="K6" t="n">
-        <v>62.26920516030602</v>
+        <v>62.26920832315121</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75993212439892</v>
+        <v>42.75993497348746</v>
       </c>
       <c r="M6" t="n">
-        <v>37.99697594089669</v>
+        <v>37.9969750685003</v>
       </c>
       <c r="N6" t="n">
-        <v>74.95037671475228</v>
+        <v>74.95035405100529</v>
       </c>
       <c r="O6" t="n">
-        <v>56.62665623510724</v>
+        <v>56.62665326279497</v>
       </c>
       <c r="P6" t="n">
-        <v>29.28534724045534</v>
+        <v>29.28534620215771</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.24156417892831</v>
+        <v>24.24155499179383</v>
       </c>
       <c r="R6" t="n">
-        <v>18.92807506493136</v>
+        <v>18.92805612295989</v>
       </c>
       <c r="S6" t="n">
-        <v>26.56137866691916</v>
+        <v>26.5613618905067</v>
       </c>
     </row>
     <row r="7">
@@ -840,55 +840,55 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>10.97567515959276</v>
+        <v>14.30691959951558</v>
       </c>
       <c r="D7" t="n">
-        <v>14.30692143381022</v>
+        <v>10.97567210347772</v>
       </c>
       <c r="E7" t="n">
-        <v>26.97617996143049</v>
+        <v>26.97620763380961</v>
       </c>
       <c r="F7" t="n">
-        <v>12.71268404296229</v>
+        <v>12.71269330939227</v>
       </c>
       <c r="G7" t="n">
-        <v>9.586011059787202</v>
+        <v>9.586012051593574</v>
       </c>
       <c r="H7" t="n">
-        <v>80.60984066773732</v>
+        <v>80.60983890825551</v>
       </c>
       <c r="I7" t="n">
-        <v>74.33392820741403</v>
+        <v>74.33394406266908</v>
       </c>
       <c r="J7" t="n">
-        <v>65.86128035487417</v>
+        <v>65.86129888519548</v>
       </c>
       <c r="K7" t="n">
-        <v>64.17768886625905</v>
+        <v>64.1777017204667</v>
       </c>
       <c r="L7" t="n">
-        <v>35.66327174513773</v>
+        <v>35.66328892642692</v>
       </c>
       <c r="M7" t="n">
-        <v>28.58039183307035</v>
+        <v>28.58040026426753</v>
       </c>
       <c r="N7" t="n">
-        <v>74.63399174155951</v>
+        <v>74.63399253437439</v>
       </c>
       <c r="O7" t="n">
-        <v>63.794146186318</v>
+        <v>63.79415095318225</v>
       </c>
       <c r="P7" t="n">
-        <v>20.1036727148358</v>
+        <v>20.10368178901848</v>
       </c>
       <c r="Q7" t="n">
-        <v>19.35177636448925</v>
+        <v>19.35179461434941</v>
       </c>
       <c r="R7" t="n">
-        <v>18.52823854271692</v>
+        <v>18.52826683590086</v>
       </c>
       <c r="S7" t="n">
-        <v>18.86491593461702</v>
+        <v>18.86492076453776</v>
       </c>
     </row>
     <row r="8">
@@ -901,55 +901,55 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>7.094512400263013</v>
+        <v>11.91697306688317</v>
       </c>
       <c r="D8" t="n">
-        <v>11.9169741268015</v>
+        <v>7.094512107707359</v>
       </c>
       <c r="E8" t="n">
-        <v>34.58458689433927</v>
+        <v>34.58462098585942</v>
       </c>
       <c r="F8" t="n">
-        <v>17.39673246108812</v>
+        <v>17.39673570861961</v>
       </c>
       <c r="G8" t="n">
-        <v>11.4109494985453</v>
+        <v>11.41095328631266</v>
       </c>
       <c r="H8" t="n">
-        <v>97.87541931532645</v>
+        <v>97.87542035578794</v>
       </c>
       <c r="I8" t="n">
-        <v>88.68199562956028</v>
+        <v>88.68199242540372</v>
       </c>
       <c r="J8" t="n">
-        <v>68.84938567673808</v>
+        <v>68.84939050450451</v>
       </c>
       <c r="K8" t="n">
-        <v>71.00939375885329</v>
+        <v>71.00939016538568</v>
       </c>
       <c r="L8" t="n">
-        <v>40.93781969187907</v>
+        <v>40.93781122284466</v>
       </c>
       <c r="M8" t="n">
-        <v>33.07906006240307</v>
+        <v>33.07907075765909</v>
       </c>
       <c r="N8" t="n">
-        <v>91.31836744450864</v>
+        <v>91.3183674334074</v>
       </c>
       <c r="O8" t="n">
-        <v>68.41638768814549</v>
+        <v>68.41639383335828</v>
       </c>
       <c r="P8" t="n">
-        <v>29.65610144164475</v>
+        <v>29.65609725687062</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.03177669088692</v>
+        <v>25.03177515978582</v>
       </c>
       <c r="R8" t="n">
-        <v>19.92806064550965</v>
+        <v>19.92806180452434</v>
       </c>
       <c r="S8" t="n">
-        <v>25.07926980875996</v>
+        <v>25.07926307021426</v>
       </c>
     </row>
     <row r="9">
@@ -962,55 +962,55 @@
         <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>14.91349114202216</v>
+        <v>23.80466653885151</v>
       </c>
       <c r="D9" t="n">
-        <v>23.80467389713466</v>
+        <v>14.91349379370913</v>
       </c>
       <c r="E9" t="n">
-        <v>21.18644331280572</v>
+        <v>21.18649399843502</v>
       </c>
       <c r="F9" t="n">
-        <v>14.65915381242098</v>
+        <v>14.6591504783342</v>
       </c>
       <c r="G9" t="n">
-        <v>11.80485361918487</v>
+        <v>11.80485364663808</v>
       </c>
       <c r="H9" t="n">
-        <v>83.98922583489974</v>
+        <v>83.98920301197174</v>
       </c>
       <c r="I9" t="n">
-        <v>77.03538512896996</v>
+        <v>77.03537802899214</v>
       </c>
       <c r="J9" t="n">
-        <v>70.90263717640809</v>
+        <v>70.90262031896002</v>
       </c>
       <c r="K9" t="n">
-        <v>65.94596087551727</v>
+        <v>65.94594572901983</v>
       </c>
       <c r="L9" t="n">
-        <v>40.73065891729799</v>
+        <v>40.73066496109748</v>
       </c>
       <c r="M9" t="n">
-        <v>35.53664797286978</v>
+        <v>35.53664576307298</v>
       </c>
       <c r="N9" t="n">
-        <v>78.60411548939624</v>
+        <v>78.60410006676135</v>
       </c>
       <c r="O9" t="n">
-        <v>66.27243650820967</v>
+        <v>66.27241651840662</v>
       </c>
       <c r="P9" t="n">
-        <v>17.55689898504541</v>
+        <v>17.55687783748051</v>
       </c>
       <c r="Q9" t="n">
-        <v>17.14186436260475</v>
+        <v>17.14185431762007</v>
       </c>
       <c r="R9" t="n">
-        <v>16.68936533796677</v>
+        <v>16.68936747902518</v>
       </c>
       <c r="S9" t="n">
-        <v>18.30824954436951</v>
+        <v>18.30822368720252</v>
       </c>
     </row>
     <row r="10">
@@ -1023,55 +1023,55 @@
         <v>199</v>
       </c>
       <c r="C10" t="n">
-        <v>10.96966827669193</v>
+        <v>15.38408405739601</v>
       </c>
       <c r="D10" t="n">
-        <v>15.38407554653299</v>
+        <v>10.96966790818701</v>
       </c>
       <c r="E10" t="n">
-        <v>36.42042157392604</v>
+        <v>36.42043616359849</v>
       </c>
       <c r="F10" t="n">
-        <v>13.38670732420702</v>
+        <v>13.38671352632386</v>
       </c>
       <c r="G10" t="n">
-        <v>8.511212081863192</v>
+        <v>8.511214072065275</v>
       </c>
       <c r="H10" t="n">
-        <v>79.69721588074901</v>
+        <v>79.69721052713258</v>
       </c>
       <c r="I10" t="n">
-        <v>76.92825555132085</v>
+        <v>76.92826835386039</v>
       </c>
       <c r="J10" t="n">
-        <v>64.51699627687591</v>
+        <v>64.51699385453456</v>
       </c>
       <c r="K10" t="n">
-        <v>66.9256478304809</v>
+        <v>66.92562671285997</v>
       </c>
       <c r="L10" t="n">
-        <v>36.65652079261696</v>
+        <v>36.65653416456217</v>
       </c>
       <c r="M10" t="n">
-        <v>26.00845787615624</v>
+        <v>26.00846044031225</v>
       </c>
       <c r="N10" t="n">
-        <v>76.96540477170315</v>
+        <v>76.96540067589525</v>
       </c>
       <c r="O10" t="n">
-        <v>64.23860497366371</v>
+        <v>64.23860188574461</v>
       </c>
       <c r="P10" t="n">
-        <v>19.04736500028717</v>
+        <v>19.04736260176882</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.8112156537101</v>
+        <v>16.81122687942827</v>
       </c>
       <c r="R10" t="n">
-        <v>15.44218002096692</v>
+        <v>15.44218680703856</v>
       </c>
       <c r="S10" t="n">
-        <v>17.84356264001272</v>
+        <v>17.84356454743816</v>
       </c>
     </row>
     <row r="11">
@@ -1084,55 +1084,55 @@
         <v>100</v>
       </c>
       <c r="C11" t="n">
+        <v>19.47274853112122</v>
+      </c>
+      <c r="D11" t="n">
         <v>8.136760284409215</v>
       </c>
-      <c r="D11" t="n">
-        <v>19.47275988397671</v>
-      </c>
       <c r="E11" t="n">
-        <v>23.0616683536931</v>
+        <v>23.06167527726724</v>
       </c>
       <c r="F11" t="n">
-        <v>15.06127075231269</v>
+        <v>15.06127210613602</v>
       </c>
       <c r="G11" t="n">
-        <v>11.58789044156256</v>
+        <v>11.5878904403933</v>
       </c>
       <c r="H11" t="n">
-        <v>83.5448932992204</v>
+        <v>83.54490329891577</v>
       </c>
       <c r="I11" t="n">
-        <v>71.21135087060996</v>
+        <v>71.21135402477137</v>
       </c>
       <c r="J11" t="n">
-        <v>69.14932398977041</v>
+        <v>69.14932841206665</v>
       </c>
       <c r="K11" t="n">
-        <v>64.34642433149911</v>
+        <v>64.34641100338536</v>
       </c>
       <c r="L11" t="n">
-        <v>42.99566939086458</v>
+        <v>42.99567662263136</v>
       </c>
       <c r="M11" t="n">
-        <v>33.16333436725849</v>
+        <v>33.16334158835749</v>
       </c>
       <c r="N11" t="n">
-        <v>75.53232505315412</v>
+        <v>75.53230533295937</v>
       </c>
       <c r="O11" t="n">
-        <v>63.92562022780069</v>
+        <v>63.9256247224416</v>
       </c>
       <c r="P11" t="n">
-        <v>17.26400682183328</v>
+        <v>17.26400994402088</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.98358501779227</v>
+        <v>13.98360047354867</v>
       </c>
       <c r="R11" t="n">
-        <v>10.17380175464488</v>
+        <v>10.17382964322233</v>
       </c>
       <c r="S11" t="n">
-        <v>15.3665398452722</v>
+        <v>15.36651179830076</v>
       </c>
     </row>
     <row r="12">
@@ -1145,55 +1145,55 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>9.27981759860784</v>
+        <v>16.66302406698498</v>
       </c>
       <c r="D12" t="n">
-        <v>16.66302091497436</v>
+        <v>9.27983133268061</v>
       </c>
       <c r="E12" t="n">
-        <v>32.18721580963284</v>
+        <v>32.18716191445922</v>
       </c>
       <c r="F12" t="n">
-        <v>13.72607014189635</v>
+        <v>13.72606542573238</v>
       </c>
       <c r="G12" t="n">
-        <v>9.831505365724452</v>
+        <v>9.831503640921216</v>
       </c>
       <c r="H12" t="n">
-        <v>73.63009130280479</v>
+        <v>73.63007954733611</v>
       </c>
       <c r="I12" t="n">
-        <v>71.37489597614648</v>
+        <v>71.37487690748185</v>
       </c>
       <c r="J12" t="n">
-        <v>57.42500975647528</v>
+        <v>57.42502296421969</v>
       </c>
       <c r="K12" t="n">
-        <v>61.28002214493949</v>
+        <v>61.28003822734781</v>
       </c>
       <c r="L12" t="n">
-        <v>43.11222890853102</v>
+        <v>43.11222737736167</v>
       </c>
       <c r="M12" t="n">
-        <v>31.46759364687345</v>
+        <v>31.46759501231202</v>
       </c>
       <c r="N12" t="n">
-        <v>69.78259847388455</v>
+        <v>69.78258314321559</v>
       </c>
       <c r="O12" t="n">
-        <v>57.10256650241897</v>
+        <v>57.10255316123884</v>
       </c>
       <c r="P12" t="n">
-        <v>28.18176816745826</v>
+        <v>28.1817779932307</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.27177557301074</v>
+        <v>21.27175855813899</v>
       </c>
       <c r="R12" t="n">
-        <v>16.57634450658256</v>
+        <v>16.57636265009607</v>
       </c>
       <c r="S12" t="n">
-        <v>18.17076498836734</v>
+        <v>18.17076612935548</v>
       </c>
     </row>
     <row r="13">
@@ -1206,55 +1206,55 @@
         <v>111</v>
       </c>
       <c r="C13" t="n">
-        <v>8.029082590720487</v>
+        <v>12.53084377026197</v>
       </c>
       <c r="D13" t="n">
-        <v>12.53085103598142</v>
+        <v>8.029086585094857</v>
       </c>
       <c r="E13" t="n">
-        <v>20.08995950391001</v>
+        <v>20.08997336973426</v>
       </c>
       <c r="F13" t="n">
-        <v>14.59918158724888</v>
+        <v>14.59918414522006</v>
       </c>
       <c r="G13" t="n">
-        <v>11.72226283089259</v>
+        <v>11.72226600863272</v>
       </c>
       <c r="H13" t="n">
-        <v>86.83168511167597</v>
+        <v>86.8316866146198</v>
       </c>
       <c r="I13" t="n">
-        <v>81.91170503039575</v>
+        <v>81.911688012765</v>
       </c>
       <c r="J13" t="n">
-        <v>77.31958437614296</v>
+        <v>77.3195811164114</v>
       </c>
       <c r="K13" t="n">
         <v>75.65635312153312</v>
       </c>
       <c r="L13" t="n">
-        <v>38.04005607961406</v>
+        <v>38.04005620523316</v>
       </c>
       <c r="M13" t="n">
-        <v>30.07473546493593</v>
+        <v>30.07473984182345</v>
       </c>
       <c r="N13" t="n">
-        <v>82.5815302678761</v>
+        <v>82.58152218544107</v>
       </c>
       <c r="O13" t="n">
-        <v>75.02524734646056</v>
+        <v>75.0252243984342</v>
       </c>
       <c r="P13" t="n">
-        <v>11.74781064164132</v>
+        <v>11.74781511274141</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.48276258001961</v>
+        <v>10.48275757404024</v>
       </c>
       <c r="R13" t="n">
-        <v>9.141781533107761</v>
+        <v>9.141766320847504</v>
       </c>
       <c r="S13" t="n">
-        <v>10.83919658984549</v>
+        <v>10.83919473937948</v>
       </c>
     </row>
     <row r="14">
@@ -1267,55 +1267,55 @@
         <v>135</v>
       </c>
       <c r="C14" t="n">
-        <v>11.85275227484968</v>
+        <v>19.8701526001714</v>
       </c>
       <c r="D14" t="n">
-        <v>19.87015244208916</v>
+        <v>11.85275770545421</v>
       </c>
       <c r="E14" t="n">
-        <v>35.07999085402093</v>
+        <v>35.08001716279445</v>
       </c>
       <c r="F14" t="n">
-        <v>13.56279079103879</v>
+        <v>13.56279001742477</v>
       </c>
       <c r="G14" t="n">
-        <v>9.872107448887574</v>
+        <v>9.872108993128743</v>
       </c>
       <c r="H14" t="n">
-        <v>79.66308781649093</v>
+        <v>79.66308207213544</v>
       </c>
       <c r="I14" t="n">
-        <v>72.8289844650065</v>
+        <v>72.82897071940329</v>
       </c>
       <c r="J14" t="n">
-        <v>64.69731279149946</v>
+        <v>64.6973297512245</v>
       </c>
       <c r="K14" t="n">
-        <v>62.41748991772631</v>
+        <v>62.41747428808139</v>
       </c>
       <c r="L14" t="n">
-        <v>41.23008857683926</v>
+        <v>41.23008179609723</v>
       </c>
       <c r="M14" t="n">
-        <v>30.46571079846989</v>
+        <v>30.4657091407841</v>
       </c>
       <c r="N14" t="n">
-        <v>73.57283916039471</v>
+        <v>73.57283715953923</v>
       </c>
       <c r="O14" t="n">
-        <v>61.43472928776436</v>
+        <v>61.43474511064594</v>
       </c>
       <c r="P14" t="n">
-        <v>21.67258681991242</v>
+        <v>21.67258474028365</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.70468034631764</v>
+        <v>20.70468483270723</v>
       </c>
       <c r="R14" t="n">
-        <v>19.60680078089807</v>
+        <v>19.60681284296985</v>
       </c>
       <c r="S14" t="n">
-        <v>21.75590042859427</v>
+        <v>21.75590233517882</v>
       </c>
     </row>
     <row r="15">
@@ -1328,55 +1328,55 @@
         <v>990</v>
       </c>
       <c r="C15" t="n">
-        <v>10.54158728333348</v>
+        <v>17.95061129190851</v>
       </c>
       <c r="D15" t="n">
-        <v>17.95061030514558</v>
+        <v>10.54159385425377</v>
       </c>
       <c r="E15" t="n">
-        <v>31.7396119210708</v>
+        <v>31.73961997334066</v>
       </c>
       <c r="F15" t="n">
-        <v>14.25203785388745</v>
+        <v>14.25203448784581</v>
       </c>
       <c r="G15" t="n">
-        <v>10.77539605676618</v>
+        <v>10.77540016150175</v>
       </c>
       <c r="H15" t="n">
-        <v>75.20639013310408</v>
+        <v>75.20637312812711</v>
       </c>
       <c r="I15" t="n">
-        <v>66.14816748460497</v>
+        <v>66.14815276443549</v>
       </c>
       <c r="J15" t="n">
-        <v>56.63438889329179</v>
+        <v>56.63437616147718</v>
       </c>
       <c r="K15" t="n">
-        <v>58.45034682199331</v>
+        <v>58.45035532790402</v>
       </c>
       <c r="L15" t="n">
         <v>43.32672475848042</v>
       </c>
       <c r="M15" t="n">
-        <v>38.19007802060123</v>
+        <v>38.19008026298417</v>
       </c>
       <c r="N15" t="n">
-        <v>67.42765990035338</v>
+        <v>67.42764319656152</v>
       </c>
       <c r="O15" t="n">
-        <v>54.96320545441405</v>
+        <v>54.9632130311562</v>
       </c>
       <c r="P15" t="n">
-        <v>25.17666139722934</v>
+        <v>25.17666010333443</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.08490181086696</v>
+        <v>20.08490689771197</v>
       </c>
       <c r="R15" t="n">
-        <v>14.56276064564639</v>
+        <v>14.56277333883366</v>
       </c>
       <c r="S15" t="n">
-        <v>20.49776824034391</v>
+        <v>20.49777583370812</v>
       </c>
     </row>
     <row r="16">
@@ -1389,55 +1389,55 @@
         <v>920</v>
       </c>
       <c r="C16" t="n">
-        <v>12.69386362185776</v>
+        <v>23.31917368864223</v>
       </c>
       <c r="D16" t="n">
-        <v>23.31916611182676</v>
+        <v>12.69385254486453</v>
       </c>
       <c r="E16" t="n">
-        <v>35.95205943739185</v>
+        <v>35.95206839358333</v>
       </c>
       <c r="F16" t="n">
-        <v>8.643519253747877</v>
+        <v>8.643516450303981</v>
       </c>
       <c r="G16" t="n">
-        <v>6.289461200034208</v>
+        <v>6.289457921342248</v>
       </c>
       <c r="H16" t="n">
-        <v>70.03722597536442</v>
+        <v>70.03722586752336</v>
       </c>
       <c r="I16" t="n">
-        <v>67.05842781522479</v>
+        <v>67.05841889047117</v>
       </c>
       <c r="J16" t="n">
-        <v>51.2168444917183</v>
+        <v>51.21683714291676</v>
       </c>
       <c r="K16" t="n">
-        <v>50.87442441880501</v>
+        <v>50.87443283122625</v>
       </c>
       <c r="L16" t="n">
-        <v>28.97824894760298</v>
+        <v>28.97825018358314</v>
       </c>
       <c r="M16" t="n">
-        <v>19.08672971772493</v>
+        <v>19.08672052060823</v>
       </c>
       <c r="N16" t="n">
-        <v>67.32349620129159</v>
+        <v>67.32349094342804</v>
       </c>
       <c r="O16" t="n">
-        <v>49.64208188923231</v>
+        <v>49.64208447889506</v>
       </c>
       <c r="P16" t="n">
-        <v>27.31319061464886</v>
+        <v>27.3132133976257</v>
       </c>
       <c r="Q16" t="n">
-        <v>26.99848163669811</v>
+        <v>26.99849683560221</v>
       </c>
       <c r="R16" t="n">
-        <v>26.67649247954594</v>
+        <v>26.67649986640894</v>
       </c>
       <c r="S16" t="n">
-        <v>28.11803120314135</v>
+        <v>28.11804677231455</v>
       </c>
     </row>
   </sheetData>
